--- a/KURIKULUM2026_REVISI/026_ANALISIS_KRITIS_MK_DIHAPUS_DAN_REKOMENDASI_PENGGANTI.xlsx
+++ b/KURIKULUM2026_REVISI/026_ANALISIS_KRITIS_MK_DIHAPUS_DAN_REKOMENDASI_PENGGANTI.xlsx
@@ -813,7 +813,7 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>`STI-626` Deep Learning &amp; Neural Networks</t>
+          <t>`STI-726` Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>`STI-626` Deep Learning &amp; Neural Networks</t>
+          <t>`STI-726` Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>"bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016. Unsur ekstraksi fitur sinyal terserap parsial pada `STI-626` Deep Learning &amp; `STA-703` Smart Surveillance"</t>
+          <t>"bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016. Unsur ekstraksi fitur sinyal terserap parsial pada `STI-726` Deep Learning &amp; `STA-703` Smart Surveillance"</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
